--- a/Data/DungeonExperience.xlsx
+++ b/Data/DungeonExperience.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F07FC513-2C03-4EDE-94AA-B4F3F9B63D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668F4ECB-B1A9-4CCC-937D-CF213EAA7D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="4110" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonExperience" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="119">
   <si>
     <t>1000;1001;</t>
   </si>
@@ -68,15 +67,6 @@
     <t>ExtraTimeOnSupportKill</t>
   </si>
   <si>
-    <t>RewardExp</t>
-  </si>
-  <si>
-    <t>RewardPointType1</t>
-  </si>
-  <si>
-    <t>RewardPointAmount1</t>
-  </si>
-  <si>
     <t>KillCountWithTimeBonus</t>
   </si>
   <si>
@@ -86,9 +76,6 @@
     <t>1000;</t>
   </si>
   <si>
-    <t>Gold</t>
-  </si>
-  <si>
     <t>EXP 2</t>
   </si>
   <si>
@@ -237,6 +224,160 @@
   </si>
   <si>
     <t>EXP 50</t>
+  </si>
+  <si>
+    <t>RewardPoints</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp=420</t>
+  </si>
+  <si>
+    <t>Exp=540</t>
+  </si>
+  <si>
+    <t>Exp=660</t>
+  </si>
+  <si>
+    <t>Exp=780</t>
+  </si>
+  <si>
+    <t>Exp=900</t>
+  </si>
+  <si>
+    <t>Exp=1020</t>
+  </si>
+  <si>
+    <t>Exp=1140</t>
+  </si>
+  <si>
+    <t>Exp=1260</t>
+  </si>
+  <si>
+    <t>Exp=1380</t>
+  </si>
+  <si>
+    <t>Exp=1500</t>
+  </si>
+  <si>
+    <t>Exp=1620</t>
+  </si>
+  <si>
+    <t>Exp=1740</t>
+  </si>
+  <si>
+    <t>Exp=1860</t>
+  </si>
+  <si>
+    <t>Exp=1980</t>
+  </si>
+  <si>
+    <t>Exp=2100</t>
+  </si>
+  <si>
+    <t>Exp=2220</t>
+  </si>
+  <si>
+    <t>Exp=2340</t>
+  </si>
+  <si>
+    <t>Exp=2460</t>
+  </si>
+  <si>
+    <t>Exp=2580</t>
+  </si>
+  <si>
+    <t>Exp=2700</t>
+  </si>
+  <si>
+    <t>Exp=2820</t>
+  </si>
+  <si>
+    <t>Exp=2940</t>
+  </si>
+  <si>
+    <t>Exp=3060</t>
+  </si>
+  <si>
+    <t>Exp=3180</t>
+  </si>
+  <si>
+    <t>Exp=3300</t>
+  </si>
+  <si>
+    <t>Exp=3420</t>
+  </si>
+  <si>
+    <t>Exp=3540</t>
+  </si>
+  <si>
+    <t>Exp=3660</t>
+  </si>
+  <si>
+    <t>Exp=3780</t>
+  </si>
+  <si>
+    <t>Exp=3900</t>
+  </si>
+  <si>
+    <t>Exp=4020</t>
+  </si>
+  <si>
+    <t>Exp=4140</t>
+  </si>
+  <si>
+    <t>Exp=4260</t>
+  </si>
+  <si>
+    <t>Exp=4380</t>
+  </si>
+  <si>
+    <t>Exp=4500</t>
+  </si>
+  <si>
+    <t>Exp=4620</t>
+  </si>
+  <si>
+    <t>Exp=4740</t>
+  </si>
+  <si>
+    <t>Exp=4860</t>
+  </si>
+  <si>
+    <t>Exp=4980</t>
+  </si>
+  <si>
+    <t>Exp=5100</t>
+  </si>
+  <si>
+    <t>Exp=5220</t>
+  </si>
+  <si>
+    <t>Exp=5340</t>
+  </si>
+  <si>
+    <t>Exp=5460</t>
+  </si>
+  <si>
+    <t>Exp=5580</t>
+  </si>
+  <si>
+    <t>Exp=5700</t>
+  </si>
+  <si>
+    <t>Exp=5820</t>
+  </si>
+  <si>
+    <t>Exp=5940</t>
+  </si>
+  <si>
+    <t>Exp=6060</t>
+  </si>
+  <si>
+    <t>Exp=6180</t>
+  </si>
+  <si>
+    <t>Exp=6300</t>
   </si>
 </sst>
 </file>
@@ -583,10 +724,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -630,30 +771,24 @@
         <v>14</v>
       </c>
       <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
       </c>
       <c r="D2">
         <v>100001</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -682,31 +817,25 @@
       <c r="N2">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O2">
-        <v>420</v>
-      </c>
-      <c r="P2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
       </c>
       <c r="D3">
         <v>100002</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -735,25 +864,19 @@
       <c r="N3">
         <v>2.1</v>
       </c>
-      <c r="O3">
-        <v>540</v>
-      </c>
-      <c r="P3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>100003</v>
@@ -788,31 +911,25 @@
       <c r="N4">
         <v>2.15</v>
       </c>
-      <c r="O4">
-        <v>660</v>
-      </c>
-      <c r="P4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q4">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>100004</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>11</v>
@@ -841,31 +958,25 @@
       <c r="N5">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O5">
-        <v>780</v>
-      </c>
-      <c r="P5" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q5">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>100005</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -894,25 +1005,19 @@
       <c r="N6">
         <v>2.25</v>
       </c>
-      <c r="O6">
-        <v>900</v>
-      </c>
-      <c r="P6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>100006</v>
@@ -947,31 +1052,25 @@
       <c r="N7">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O7">
-        <v>1020</v>
-      </c>
-      <c r="P7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>100007</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>12</v>
@@ -1000,31 +1099,25 @@
       <c r="N8">
         <v>2.35</v>
       </c>
-      <c r="O8">
-        <v>1140</v>
-      </c>
-      <c r="P8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q8">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>100008</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F9">
         <v>12</v>
@@ -1053,25 +1146,19 @@
       <c r="N9">
         <v>2.4</v>
       </c>
-      <c r="O9">
-        <v>1260</v>
-      </c>
-      <c r="P9" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q9">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>100009</v>
@@ -1106,31 +1193,25 @@
       <c r="N10">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O10">
-        <v>1380</v>
-      </c>
-      <c r="P10" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>100010</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>13</v>
@@ -1159,31 +1240,25 @@
       <c r="N11">
         <v>2.5</v>
       </c>
-      <c r="O11">
-        <v>1500</v>
-      </c>
-      <c r="P11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>100011</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F12">
         <v>13</v>
@@ -1212,25 +1287,19 @@
       <c r="N12">
         <v>2.5499999999999998</v>
       </c>
-      <c r="O12">
-        <v>1620</v>
-      </c>
-      <c r="P12" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q12">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>100012</v>
@@ -1265,31 +1334,25 @@
       <c r="N13">
         <v>2.6</v>
       </c>
-      <c r="O13">
-        <v>1740</v>
-      </c>
-      <c r="P13" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <v>100013</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F14">
         <v>14</v>
@@ -1318,31 +1381,25 @@
       <c r="N14">
         <v>2.65</v>
       </c>
-      <c r="O14">
-        <v>1860</v>
-      </c>
-      <c r="P14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <v>100014</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -1371,25 +1428,19 @@
       <c r="N15">
         <v>2.7</v>
       </c>
-      <c r="O15">
-        <v>1980</v>
-      </c>
-      <c r="P15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>100015</v>
@@ -1424,31 +1475,25 @@
       <c r="N16">
         <v>2.75</v>
       </c>
-      <c r="O16">
-        <v>2100</v>
-      </c>
-      <c r="P16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>100016</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F17">
         <v>15</v>
@@ -1477,31 +1522,25 @@
       <c r="N17">
         <v>2.8</v>
       </c>
-      <c r="O17">
-        <v>2220</v>
-      </c>
-      <c r="P17" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q17">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>100017</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F18">
         <v>15</v>
@@ -1530,25 +1569,19 @@
       <c r="N18">
         <v>2.85</v>
       </c>
-      <c r="O18">
-        <v>2340</v>
-      </c>
-      <c r="P18" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q18">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D19">
         <v>100018</v>
@@ -1583,31 +1616,25 @@
       <c r="N19">
         <v>2.9</v>
       </c>
-      <c r="O19">
-        <v>2460</v>
-      </c>
-      <c r="P19" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <v>100019</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F20">
         <v>16</v>
@@ -1636,31 +1663,25 @@
       <c r="N20">
         <v>2.95</v>
       </c>
-      <c r="O20">
-        <v>2580</v>
-      </c>
-      <c r="P20" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q20">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D21">
         <v>100020</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <v>16</v>
@@ -1689,25 +1710,19 @@
       <c r="N21">
         <v>3</v>
       </c>
-      <c r="O21">
-        <v>2700</v>
-      </c>
-      <c r="P21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q21">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D22">
         <v>100021</v>
@@ -1742,31 +1757,25 @@
       <c r="N22">
         <v>3.05</v>
       </c>
-      <c r="O22">
-        <v>2820</v>
-      </c>
-      <c r="P22" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q22">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D23">
         <v>100022</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F23">
         <v>17</v>
@@ -1795,31 +1804,25 @@
       <c r="N23">
         <v>3.1</v>
       </c>
-      <c r="O23">
-        <v>2940</v>
-      </c>
-      <c r="P23" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q23">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D24">
         <v>100023</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F24">
         <v>17</v>
@@ -1848,25 +1851,19 @@
       <c r="N24">
         <v>3.15</v>
       </c>
-      <c r="O24">
-        <v>3060</v>
-      </c>
-      <c r="P24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q24">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D25">
         <v>100024</v>
@@ -1901,31 +1898,25 @@
       <c r="N25">
         <v>3.2</v>
       </c>
-      <c r="O25">
-        <v>3180</v>
-      </c>
-      <c r="P25" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D26">
         <v>100025</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F26">
         <v>18</v>
@@ -1954,31 +1945,25 @@
       <c r="N26">
         <v>3.25</v>
       </c>
-      <c r="O26">
-        <v>3300</v>
-      </c>
-      <c r="P26" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D27">
         <v>100026</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F27">
         <v>18</v>
@@ -2007,25 +1992,19 @@
       <c r="N27">
         <v>3.3</v>
       </c>
-      <c r="O27">
-        <v>3420</v>
-      </c>
-      <c r="P27" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q27">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D28">
         <v>100027</v>
@@ -2060,31 +2039,25 @@
       <c r="N28">
         <v>3.35</v>
       </c>
-      <c r="O28">
-        <v>3540</v>
-      </c>
-      <c r="P28" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q28">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D29">
         <v>100028</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F29">
         <v>19</v>
@@ -2113,31 +2086,25 @@
       <c r="N29">
         <v>3.4</v>
       </c>
-      <c r="O29">
-        <v>3660</v>
-      </c>
-      <c r="P29" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q29">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D30">
         <v>100029</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F30">
         <v>19</v>
@@ -2166,25 +2133,19 @@
       <c r="N30">
         <v>3.45</v>
       </c>
-      <c r="O30">
-        <v>3780</v>
-      </c>
-      <c r="P30" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q30">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D31">
         <v>100030</v>
@@ -2219,31 +2180,25 @@
       <c r="N31">
         <v>3.5</v>
       </c>
-      <c r="O31">
-        <v>3900</v>
-      </c>
-      <c r="P31" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D32">
         <v>100031</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F32">
         <v>20</v>
@@ -2272,31 +2227,25 @@
       <c r="N32">
         <v>3.55</v>
       </c>
-      <c r="O32">
-        <v>4020</v>
-      </c>
-      <c r="P32" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q32">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D33">
         <v>100032</v>
       </c>
       <c r="E33" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F33">
         <v>20</v>
@@ -2325,25 +2274,19 @@
       <c r="N33">
         <v>3.6</v>
       </c>
-      <c r="O33">
-        <v>4140</v>
-      </c>
-      <c r="P33" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q33">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D34">
         <v>100033</v>
@@ -2378,31 +2321,25 @@
       <c r="N34">
         <v>3.65</v>
       </c>
-      <c r="O34">
-        <v>4260</v>
-      </c>
-      <c r="P34" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q34">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D35">
         <v>100034</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F35">
         <v>21</v>
@@ -2431,31 +2368,25 @@
       <c r="N35">
         <v>3.7</v>
       </c>
-      <c r="O35">
-        <v>4380</v>
-      </c>
-      <c r="P35" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q35">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D36">
         <v>100035</v>
       </c>
       <c r="E36" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F36">
         <v>21</v>
@@ -2484,25 +2415,19 @@
       <c r="N36">
         <v>3.75</v>
       </c>
-      <c r="O36">
-        <v>4500</v>
-      </c>
-      <c r="P36" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q36">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O36" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D37">
         <v>100036</v>
@@ -2537,31 +2462,25 @@
       <c r="N37">
         <v>3.8</v>
       </c>
-      <c r="O37">
-        <v>4620</v>
-      </c>
-      <c r="P37" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q37">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O37" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D38">
         <v>100037</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F38">
         <v>22</v>
@@ -2590,31 +2509,25 @@
       <c r="N38">
         <v>3.85</v>
       </c>
-      <c r="O38">
-        <v>4740</v>
-      </c>
-      <c r="P38" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q38">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D39">
         <v>100038</v>
       </c>
       <c r="E39" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F39">
         <v>22</v>
@@ -2643,25 +2556,19 @@
       <c r="N39">
         <v>3.9</v>
       </c>
-      <c r="O39">
-        <v>4860</v>
-      </c>
-      <c r="P39" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q39">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O39" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D40">
         <v>100039</v>
@@ -2696,31 +2603,25 @@
       <c r="N40">
         <v>3.95</v>
       </c>
-      <c r="O40">
-        <v>4980</v>
-      </c>
-      <c r="P40" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q40">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D41">
         <v>100040</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F41">
         <v>23</v>
@@ -2749,31 +2650,25 @@
       <c r="N41">
         <v>4</v>
       </c>
-      <c r="O41">
-        <v>5100</v>
-      </c>
-      <c r="P41" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q41">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O41" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D42">
         <v>100041</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F42">
         <v>23</v>
@@ -2802,25 +2697,19 @@
       <c r="N42">
         <v>4.05</v>
       </c>
-      <c r="O42">
-        <v>5220</v>
-      </c>
-      <c r="P42" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q42">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O42" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D43">
         <v>100042</v>
@@ -2855,31 +2744,25 @@
       <c r="N43">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O43">
-        <v>5340</v>
-      </c>
-      <c r="P43" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q43">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O43" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D44">
         <v>100043</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F44">
         <v>24</v>
@@ -2908,31 +2791,25 @@
       <c r="N44">
         <v>4.1500000000000004</v>
       </c>
-      <c r="O44">
-        <v>5460</v>
-      </c>
-      <c r="P44" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q44">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D45">
         <v>100044</v>
       </c>
       <c r="E45" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F45">
         <v>24</v>
@@ -2961,25 +2838,19 @@
       <c r="N45">
         <v>4.2</v>
       </c>
-      <c r="O45">
-        <v>5580</v>
-      </c>
-      <c r="P45" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q45">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D46">
         <v>100045</v>
@@ -3014,31 +2885,25 @@
       <c r="N46">
         <v>4.25</v>
       </c>
-      <c r="O46">
-        <v>5700</v>
-      </c>
-      <c r="P46" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q46">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O46" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D47">
         <v>100046</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F47">
         <v>24</v>
@@ -3067,31 +2932,25 @@
       <c r="N47">
         <v>4.3</v>
       </c>
-      <c r="O47">
-        <v>5820</v>
-      </c>
-      <c r="P47" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q47">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D48">
         <v>100047</v>
       </c>
       <c r="E48" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F48">
         <v>24</v>
@@ -3120,25 +2979,19 @@
       <c r="N48">
         <v>4.3499999999999996</v>
       </c>
-      <c r="O48">
-        <v>5940</v>
-      </c>
-      <c r="P48" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q48">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O48" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D49">
         <v>100048</v>
@@ -3173,31 +3026,25 @@
       <c r="N49">
         <v>4.4000000000000004</v>
       </c>
-      <c r="O49">
-        <v>6060</v>
-      </c>
-      <c r="P49" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q49">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O49" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D50">
         <v>100049</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F50">
         <v>24</v>
@@ -3226,31 +3073,25 @@
       <c r="N50">
         <v>4.45</v>
       </c>
-      <c r="O50">
-        <v>6180</v>
-      </c>
-      <c r="P50" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q50">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O50" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D51">
         <v>100050</v>
       </c>
       <c r="E51" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F51">
         <v>24</v>
@@ -3279,14 +3120,8 @@
       <c r="N51">
         <v>4.5</v>
       </c>
-      <c r="O51">
-        <v>6300</v>
-      </c>
-      <c r="P51" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q51">
-        <v>760</v>
+      <c r="O51" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
